--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22034-2026 artfynd.xlsx
+++ b/artfynd/A 22034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136533056</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533059</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533062</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136534162</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136534163</v>
       </c>
       <c r="B6" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136539116</v>
       </c>
       <c r="B7" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136539123</v>
       </c>
       <c r="B8" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136539099</v>
       </c>
       <c r="B9" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
